--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.70490430446591</v>
+        <v>5.96454694947571</v>
       </c>
       <c r="D2" t="n">
-        <v>13.35747170945978</v>
+        <v>2.170589152787214</v>
       </c>
       <c r="E2" t="n">
-        <v>10.92423545881024</v>
+        <v>1.775188262056664</v>
       </c>
       <c r="F2" t="n">
-        <v>16.11418433612523</v>
+        <v>2.61855495462035</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>72.05919643955909</v>
+        <v>11.70961942142835</v>
       </c>
       <c r="D3" t="n">
-        <v>65.68181035407413</v>
+        <v>10.67329418253705</v>
       </c>
       <c r="E3" t="n">
-        <v>10.92423545881024</v>
+        <v>1.775188262056664</v>
       </c>
       <c r="F3" t="n">
-        <v>16.11418433612523</v>
+        <v>2.61855495462035</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.57259453399222</v>
+        <v>8.543046611773736</v>
       </c>
       <c r="D4" t="n">
-        <v>52.44271253780018</v>
+        <v>8.521940787392531</v>
       </c>
       <c r="E4" t="n">
-        <v>10.92423545881024</v>
+        <v>1.775188262056664</v>
       </c>
       <c r="F4" t="n">
-        <v>16.11418433612523</v>
+        <v>2.61855495462035</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>63.07997708673585</v>
+        <v>10.25049627659458</v>
       </c>
       <c r="D5" t="n">
-        <v>62.89885901148251</v>
+        <v>10.22106458936591</v>
       </c>
       <c r="E5" t="n">
-        <v>10.92423545881024</v>
+        <v>1.775188262056664</v>
       </c>
       <c r="F5" t="n">
-        <v>16.11418433612523</v>
+        <v>2.61855495462035</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.01136216933077</v>
+        <v>7.151846352516251</v>
       </c>
       <c r="D6" t="n">
-        <v>50.52801821761864</v>
+        <v>8.210802960363029</v>
       </c>
       <c r="E6" t="n">
-        <v>10.92423545881024</v>
+        <v>1.775188262056664</v>
       </c>
       <c r="F6" t="n">
-        <v>16.11418433612523</v>
+        <v>2.61855495462035</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.77848348928116</v>
+        <v>9.226503567008189</v>
       </c>
       <c r="D7" t="n">
-        <v>56.95716438346926</v>
+        <v>9.255539212313755</v>
       </c>
       <c r="E7" t="n">
-        <v>10.92423545881024</v>
+        <v>1.775188262056664</v>
       </c>
       <c r="F7" t="n">
-        <v>16.11418433612523</v>
+        <v>2.61855495462035</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>62.66533597431038</v>
+        <v>10.18311709582544</v>
       </c>
       <c r="D8" t="n">
-        <v>62.50443762799268</v>
+        <v>10.15697111454881</v>
       </c>
       <c r="E8" t="n">
-        <v>10.92423545881024</v>
+        <v>1.775188262056664</v>
       </c>
       <c r="F8" t="n">
-        <v>16.11418433612523</v>
+        <v>2.61855495462035</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>64.74921594261963</v>
+        <v>10.52174759067569</v>
       </c>
       <c r="D9" t="n">
-        <v>64.74054009847869</v>
+        <v>10.52033776600279</v>
       </c>
       <c r="E9" t="n">
-        <v>10.92423545881024</v>
+        <v>1.775188262056664</v>
       </c>
       <c r="F9" t="n">
-        <v>16.11418433612523</v>
+        <v>2.61855495462035</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
